--- a/sample_data/04_结构化字段与录入规范/标书关键字段清单.xlsx
+++ b/sample_data/04_结构化字段与录入规范/标书关键字段清单.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>基本信息</t>
+          <t>封面</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -517,7 +517,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>基本信息</t>
+          <t>封面</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -525,12 +525,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>招标人</t>
+          <t>包件号</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tenderer</t>
+          <t>package_no</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -547,7 +547,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>基本信息</t>
+          <t>封面</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -555,12 +555,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>投标人</t>
+          <t>采购人</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bidder</t>
+          <t>tenderer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -573,15 +573,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>XX铁路工程有限公司</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>基本信息</t>
+          <t>报价函</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -589,17 +585,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>项目类型</t>
+          <t>投标人</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project_type</t>
+          <t>bidder_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>下拉选项</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -607,11 +603,15 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>和远智能科技股份有限公司</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>基本信息</t>
+          <t>封面</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -619,17 +619,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>投标总价</t>
+          <t>投标总价大写</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bid_amount</t>
+          <t>bid_amount_upper</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>金额</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -638,14 +638,10 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>大于0</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>报价部分</t>
+          <t>报价</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -653,17 +649,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>工期</t>
+          <t>投标总价小写</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>duration</t>
+          <t>bid_amount_lower</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -671,15 +667,15 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>365日历天</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>大于0</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>技术部分</t>
+          <t>报价</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -705,11 +701,15 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>张方恒</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>人员部分</t>
+          <t>人员</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -717,12 +717,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>质保期</t>
+          <t>物资品种</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>warranty_period</t>
+          <t>material_type</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -737,16 +737,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>24个月</t>
+          <t>RTU及能管系统</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>商务部分</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>封面</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>模板3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
